--- a/Aug_2026/Daily Sales/29-08-26/Salman.xlsx
+++ b/Aug_2026/Daily Sales/29-08-26/Salman.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA30D5D-F105-456D-9CA2-F0D3E5E1D54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C860F398-EFEE-46F2-92CC-2FCAD580EF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="536">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1651,6 +1651,18 @@
   </si>
   <si>
     <t>Yasir Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City Mart </t>
+  </si>
+  <si>
+    <t>Address:  Pepsi Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Raya Mart </t>
+  </si>
+  <si>
+    <t>Address: Tajbagh</t>
   </si>
 </sst>
 </file>
@@ -26771,7 +26783,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -26828,7 +26840,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="400" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="B8" s="400"/>
       <c r="C8" s="400"/>
@@ -27237,18 +27249,20 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96"/>
+      <c r="H18" s="96">
+        <v>40</v>
+      </c>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2098.5</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>167.88</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -27256,19 +27270,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1857.1725000000001</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>396.61016949152526</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.268913347457627</v>
       </c>
       <c r="P18" s="311">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2265.051582838983</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -27310,18 +27324,20 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96"/>
+      <c r="H19" s="96">
+        <v>40</v>
+      </c>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>232.44800000000001</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -27329,19 +27345,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>549.15254237288138</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15.603042711864408</v>
       </c>
       <c r="P19" s="311">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3136.2115850847458</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -27382,18 +27398,20 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96"/>
+      <c r="H20" s="96">
+        <v>40</v>
+      </c>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>232.44800000000001</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -27401,24 +27419,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>549.15254237288138</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15.603042711864408</v>
       </c>
       <c r="P20" s="311">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3136.2115850847458</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>0</v>
+        <v>149.34340881355934</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -27459,18 +27477,20 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96"/>
+      <c r="H21" s="96">
+        <v>40</v>
+      </c>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>232.44800000000001</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -27478,19 +27498,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>549.15254237288138</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15.603042711864408</v>
       </c>
       <c r="P21" s="311">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3136.2115850847458</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -27748,19 +27768,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10815.300000000001</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>0</v>
+        <v>865.22399999999993</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>378.53550000000007</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -27768,19 +27788,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9571.540500000001</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>0</v>
+        <v>2044.0677966101694</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>0</v>
+        <v>58.078041483050853</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>0</v>
+        <v>11673.686338093221</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -27834,7 +27854,7 @@
       <c r="O28" s="368"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>0</v>
+        <v>10815.300000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27855,7 +27875,7 @@
       <c r="O29" s="370"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>0</v>
+        <v>865.22399999999993</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27876,7 +27896,7 @@
       <c r="O30" s="370"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>0</v>
+        <v>378.53550000000007</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27898,7 +27918,7 @@
       <c r="O31" s="370"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>0</v>
+        <v>9571.540500000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27922,7 +27942,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>0</v>
+        <v>2044.0677966101694</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27944,7 +27964,7 @@
       <c r="O33" s="372"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>0</v>
+        <v>11615.608296610171</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27969,7 +27989,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>0</v>
+        <v>58.07804148305086</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27979,7 +27999,7 @@
       <c r="O35" s="374"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>0</v>
+        <v>11673.686338093223</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29619,7 +29639,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -29676,7 +29696,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="400" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="B8" s="400"/>
       <c r="C8" s="400"/>
@@ -48013,7 +48033,7 @@
       <c r="L4" s="394"/>
       <c r="M4" s="397">
         <f ca="1">TODAY()+1</f>
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="N4" s="397"/>
       <c r="O4" s="397"/>
@@ -48041,7 +48061,7 @@
       <c r="L5" s="394"/>
       <c r="M5" s="397">
         <f ca="1">M4-1</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="N5" s="393"/>
       <c r="O5" s="393"/>
@@ -54599,19 +54619,19 @@
       </c>
       <c r="H9" s="309">
         <f>+'1'!H18+'2'!H18+'3'!H18+'4'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18+'19'!H18+'20'!H18+'21'!H18+'22'!H18+'23'!H18+'24'!H18+'25'!H18+'26'!H18+'27'!H18+'28'!H18+'29'!H18+'30'!H18</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I9" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2098.5</v>
       </c>
       <c r="J9" s="286">
         <f>+'1'!J18+'2'!J18+'3'!J18+'4'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18+'19'!J18+'20'!J18+'21'!J18+'22'!J18+'23'!J18+'24'!J18+'25'!J18+'26'!J18+'27'!J18+'28'!J18+'29'!J18+'30'!J18</f>
-        <v>0</v>
+        <v>167.88</v>
       </c>
       <c r="K9" s="286">
         <f>+'1'!K18+'2'!K18+'3'!K18+'4'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18+'11'!K18+'12'!K18+'13'!K18+'14'!K18+'15'!K18+'16'!K18+'17'!K18+'18'!K18+'19'!K18+'20'!K18+'21'!K18+'22'!K18+'23'!K18+'24'!K18+'25'!K18+'26'!K18+'27'!K18+'28'!K18+'29'!K18+'30'!K18</f>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
       <c r="L9" s="286">
         <f>+'1'!L18+'2'!L18+'3'!L18+'4'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18+'11'!L18+'12'!L18+'13'!L18+'14'!L18+'15'!L18+'16'!L18+'17'!L18+'18'!L18+'19'!L18+'20'!L18+'21'!L18+'22'!L18+'23'!L18+'24'!L18+'25'!L18+'26'!L18+'27'!L18+'28'!L18+'29'!L18+'30'!L18</f>
@@ -54619,19 +54639,19 @@
       </c>
       <c r="M9" s="230">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1857.1725000000001</v>
       </c>
       <c r="N9" s="286">
         <f>+'1'!N18+'2'!N18+'3'!N18+'4'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18+'11'!N18+'12'!N18+'13'!N18+'14'!N18+'15'!N18+'16'!N18+'17'!N18+'18'!N18+'19'!N18+'20'!N18+'21'!N18+'22'!N18+'23'!N18+'24'!N18+'25'!N18+'26'!N18+'27'!N18+'28'!N18+'29'!N18+'30'!N18</f>
-        <v>0</v>
+        <v>396.61016949152526</v>
       </c>
       <c r="O9" s="286">
         <f>+'1'!O18+'2'!O18+'3'!O18+'4'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18+'11'!O18+'12'!O18+'13'!O18+'14'!O18+'15'!O18+'16'!O18+'17'!O18+'18'!O18+'19'!O18+'20'!O18+'21'!O18+'22'!O18+'23'!O18+'24'!O18+'25'!O18+'26'!O18+'27'!O18+'28'!O18+'29'!O18+'30'!O18</f>
-        <v>0</v>
+        <v>11.268913347457627</v>
       </c>
       <c r="P9" s="311">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2265.051582838983</v>
       </c>
       <c r="Q9" s="213">
         <f>+'1'!Q18+'2'!Q18+'3'!Q18+'4'!Q18+'5'!Q18+'6'!Q18+'7'!Q18+'8'!Q18+'9'!Q18+'10'!Q18+'11'!Q18+'12'!Q18+'13'!Q18+'14'!Q18+'15'!Q18+'16'!Q18+'17'!Q18+'18'!Q18+'19'!Q18+'20'!Q18+'21'!Q18+'22'!Q18+'23'!Q18+'24'!Q18+'25'!Q18+'26'!Q18+'27'!Q18+'28'!Q18+'29'!Q18+'30'!Q18</f>
@@ -54679,19 +54699,19 @@
       </c>
       <c r="H10" s="309">
         <f>+'1'!H19+'2'!H19+'3'!H19+'4'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19+'19'!H19+'20'!H19+'21'!H19+'22'!H19+'23'!H19+'24'!H19+'25'!H19+'26'!H19+'27'!H19+'28'!H19+'29'!H19+'30'!H19</f>
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I10" s="236">
         <f t="shared" si="0"/>
-        <v>7264</v>
+        <v>10169.6</v>
       </c>
       <c r="J10" s="286">
         <f>+'1'!J19+'2'!J19+'3'!J19+'4'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19+'21'!J19+'22'!J19+'23'!J19+'24'!J19+'25'!J19+'26'!J19+'27'!J19+'28'!J19+'29'!J19+'30'!J19</f>
-        <v>581.12</v>
+        <v>813.56799999999998</v>
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
-        <v>254.24000000000004</v>
+        <v>355.93600000000004</v>
       </c>
       <c r="L10" s="286">
         <f>+'1'!L19+'2'!L19+'3'!L19+'4'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19+'11'!L19+'12'!L19+'13'!L19+'14'!L19+'15'!L19+'16'!L19+'17'!L19+'18'!L19+'19'!L19+'20'!L19+'21'!L19+'22'!L19+'23'!L19+'24'!L19+'25'!L19+'26'!L19+'27'!L19+'28'!L19+'29'!L19+'30'!L19</f>
@@ -54699,19 +54719,19 @@
       </c>
       <c r="M10" s="230">
         <f t="shared" si="1"/>
-        <v>6428.64</v>
+        <v>9000.0960000000014</v>
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
-        <v>1372.8813559322034</v>
+        <v>1922.0338983050847</v>
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>39.007606779661018</v>
+        <v>54.610649491525422</v>
       </c>
       <c r="P10" s="311">
         <f t="shared" si="2"/>
-        <v>7840.5289627118646</v>
+        <v>10976.740547796611</v>
       </c>
       <c r="Q10" s="213">
         <f>+'1'!Q19+'2'!Q19+'3'!Q19+'4'!Q19+'5'!Q19+'6'!Q19+'7'!Q19+'8'!Q19+'9'!Q19+'10'!Q19+'11'!Q19+'12'!Q19+'13'!Q19+'14'!Q19+'15'!Q19+'16'!Q19+'17'!Q19+'18'!Q19+'19'!Q19+'20'!Q19+'21'!Q19+'22'!Q19+'23'!Q19+'24'!Q19+'25'!Q19+'26'!Q19+'27'!Q19+'28'!Q19+'29'!Q19+'30'!Q19</f>
@@ -54759,19 +54779,19 @@
       </c>
       <c r="H11" s="309">
         <f>+'1'!H20+'2'!H20+'3'!H20+'4'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20+'19'!H20+'20'!H20+'21'!H20+'22'!H20+'23'!H20+'24'!H20+'25'!H20+'26'!H20+'27'!H20+'28'!H20+'29'!H20+'30'!H20</f>
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="I11" s="236">
         <f t="shared" si="0"/>
-        <v>9007.36</v>
+        <v>11912.960000000001</v>
       </c>
       <c r="J11" s="286">
         <f>+'1'!J20+'2'!J20+'3'!J20+'4'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20+'19'!J20+'20'!J20+'21'!J20+'22'!J20+'23'!J20+'24'!J20+'25'!J20+'26'!J20+'27'!J20+'28'!J20+'29'!J20+'30'!J20</f>
-        <v>720.58879999999999</v>
+        <v>953.03679999999997</v>
       </c>
       <c r="K11" s="286">
         <f>+'1'!K20+'2'!K20+'3'!K20+'4'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20+'11'!K20+'12'!K20+'13'!K20+'14'!K20+'15'!K20+'16'!K20+'17'!K20+'18'!K20+'19'!K20+'20'!K20+'21'!K20+'22'!K20+'23'!K20+'24'!K20+'25'!K20+'26'!K20+'27'!K20+'28'!K20+'29'!K20+'30'!K20</f>
-        <v>315.25760000000002</v>
+        <v>416.95360000000005</v>
       </c>
       <c r="L11" s="286">
         <f>+'1'!L20+'2'!L20+'3'!L20+'4'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20+'11'!L20+'12'!L20+'13'!L20+'14'!L20+'15'!L20+'16'!L20+'17'!L20+'18'!L20+'19'!L20+'20'!L20+'21'!L20+'22'!L20+'23'!L20+'24'!L20+'25'!L20+'26'!L20+'27'!L20+'28'!L20+'29'!L20+'30'!L20</f>
@@ -54779,19 +54799,19 @@
       </c>
       <c r="M11" s="230">
         <f t="shared" si="1"/>
-        <v>7971.5136000000002</v>
+        <v>10542.9696</v>
       </c>
       <c r="N11" s="286">
         <f>+'1'!N20+'2'!N20+'3'!N20+'4'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20+'11'!N20+'12'!N20+'13'!N20+'14'!N20+'15'!N20+'16'!N20+'17'!N20+'18'!N20+'19'!N20+'20'!N20+'21'!N20+'22'!N20+'23'!N20+'24'!N20+'25'!N20+'26'!N20+'27'!N20+'28'!N20+'29'!N20+'30'!N20</f>
-        <v>1702.3728813559323</v>
+        <v>2251.5254237288136</v>
       </c>
       <c r="O11" s="286">
         <f>+'1'!O20+'2'!O20+'3'!O20+'4'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20+'11'!O20+'12'!O20+'13'!O20+'14'!O20+'15'!O20+'16'!O20+'17'!O20+'18'!O20+'19'!O20+'20'!O20+'21'!O20+'22'!O20+'23'!O20+'24'!O20+'25'!O20+'26'!O20+'27'!O20+'28'!O20+'29'!O20+'30'!O20</f>
-        <v>48.369432406779666</v>
+        <v>63.97247511864407</v>
       </c>
       <c r="P11" s="311">
         <f t="shared" si="2"/>
-        <v>9722.2559137627122</v>
+        <v>12858.467498847458</v>
       </c>
       <c r="Q11" s="213">
         <f>+'1'!Q20+'2'!Q20+'3'!Q20+'4'!Q20+'5'!Q20+'6'!Q20+'7'!Q20+'8'!Q20+'9'!Q20+'10'!Q20+'11'!Q20+'12'!Q20+'13'!Q20+'14'!Q20+'15'!Q20+'16'!Q20+'17'!Q20+'18'!Q20+'19'!Q20+'20'!Q20+'21'!Q20+'22'!Q20+'23'!Q20+'24'!Q20+'25'!Q20+'26'!Q20+'27'!Q20+'28'!Q20+'29'!Q20+'30'!Q20</f>
@@ -54839,19 +54859,19 @@
       </c>
       <c r="H12" s="309">
         <f>+'1'!H21+'2'!H21+'3'!H21+'4'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21+'19'!H21+'20'!H21+'21'!H21+'22'!H21+'23'!H21+'24'!H21+'25'!H21+'26'!H21+'27'!H21+'28'!H21+'29'!H21+'30'!H21</f>
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="I12" s="236">
         <f t="shared" si="0"/>
-        <v>18595.84</v>
+        <v>21501.439999999999</v>
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>1487.6672000000001</v>
+        <v>1720.1152000000002</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
-        <v>650.85440000000006</v>
+        <v>752.55040000000008</v>
       </c>
       <c r="L12" s="286">
         <f>+'1'!L21+'2'!L21+'3'!L21+'4'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21+'11'!L21+'12'!L21+'13'!L21+'14'!L21+'15'!L21+'16'!L21+'17'!L21+'18'!L21+'19'!L21+'20'!L21+'21'!L21+'22'!L21+'23'!L21+'24'!L21+'25'!L21+'26'!L21+'27'!L21+'28'!L21+'29'!L21+'30'!L21</f>
@@ -54859,19 +54879,19 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>16457.3184</v>
+        <v>19028.774399999998</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
-        <v>3514.5762711864413</v>
+        <v>4063.7288135593226</v>
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>99.859473355932224</v>
+        <v>115.46251606779663</v>
       </c>
       <c r="P12" s="311">
         <f t="shared" si="2"/>
-        <v>20071.754144542374</v>
+        <v>23207.965729627118</v>
       </c>
       <c r="Q12" s="213">
         <f>+'1'!Q21+'2'!Q21+'3'!Q21+'4'!Q21+'5'!Q21+'6'!Q21+'7'!Q21+'8'!Q21+'9'!Q21+'10'!Q21+'11'!Q21+'12'!Q21+'13'!Q21+'14'!Q21+'15'!Q21+'16'!Q21+'17'!Q21+'18'!Q21+'19'!Q21+'20'!Q21+'21'!Q21+'22'!Q21+'23'!Q21+'24'!Q21+'25'!Q21+'26'!Q21+'27'!Q21+'28'!Q21+'29'!Q21+'30'!Q21</f>
@@ -55143,23 +55163,23 @@
       <c r="F16" s="357"/>
       <c r="G16" s="117">
         <f>H16/40</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H16" s="113">
         <f t="shared" ref="H16:M16" si="3">SUM(H7:H15)</f>
-        <v>560</v>
+        <v>720</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>38534.899999999994</v>
+        <v>49350.2</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>3035.7160000000003</v>
+        <v>3900.94</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>1348.7215000000001</v>
+        <v>1727.2570000000001</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
@@ -55167,19 +55187,19 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>34070.433300000004</v>
+        <v>43641.9738</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>7291.5254237288136</v>
+        <v>9335.5932203389839</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>206.80979361864408</v>
+        <v>264.88783510169492</v>
       </c>
       <c r="P16" s="113">
         <f>SUM(P7:P15)</f>
-        <v>41568.76851734746</v>
+        <v>53242.454855440679</v>
       </c>
       <c r="Q16" s="128">
         <f>SUM(Q7:Q15)</f>
@@ -55266,7 +55286,7 @@
       <c r="O19" s="368"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>38534.899999999994</v>
+        <v>49350.2</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -55298,18 +55318,18 @@
       <c r="O20" s="370"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>3035.7160000000003</v>
+        <v>3900.94</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
       </c>
       <c r="S20" s="300" t="str">
         <f>+'18'!A6:A6</f>
-        <v>Shop Name</v>
+        <v xml:space="preserve">City Mart </v>
       </c>
       <c r="T20" s="301">
         <f>+'18'!P35</f>
-        <v>0</v>
+        <v>11673.686338093223</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55330,7 +55350,7 @@
       <c r="O21" s="370"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>1428.7507000000001</v>
+        <v>1807.2862</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -55363,14 +55383,14 @@
       <c r="O22" s="370"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>34070.433299999997</v>
+        <v>43641.973799999992</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
       </c>
       <c r="S22" s="300" t="str">
         <f>+'20'!A6:A6</f>
-        <v>Shop Name</v>
+        <v xml:space="preserve">Al Raya Mart </v>
       </c>
       <c r="T22" s="301">
         <f>+'20'!P35</f>
@@ -55398,7 +55418,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>7291.5254237288136</v>
+        <v>9335.5932203389839</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -55431,7 +55451,7 @@
       <c r="O24" s="372"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>41361.958723728807</v>
+        <v>52977.567020338975</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -55467,7 +55487,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>206.80979361864408</v>
+        <v>264.88783510169492</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -55488,7 +55508,7 @@
       <c r="O26" s="374"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>41568.768517347453</v>
+        <v>53242.454855440672</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -55602,7 +55622,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>41568.76851734746</v>
+        <v>53242.454855440679</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
